--- a/data/trans_dic/P16A04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,94</t>
+          <t>1,03; 4,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,18</t>
+          <t>1,18; 5,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,4</t>
+          <t>1,72; 5,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,79</t>
+          <t>0,77; 2,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,82</t>
+          <t>0,31; 3,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,86</t>
+          <t>1,16; 4,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,38</t>
+          <t>0,32; 3,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,27</t>
+          <t>2,62; 5,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,8</t>
+          <t>0,97; 2,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,33</t>
+          <t>1,46; 4,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,72</t>
+          <t>1,39; 3,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,76</t>
+          <t>1,84; 3,79</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,93</t>
+          <t>0,28; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,71</t>
+          <t>0,77; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,82</t>
+          <t>0,83; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,99</t>
+          <t>0,74; 3,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,71</t>
+          <t>1,34; 4,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,39</t>
+          <t>0,96; 4,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,16</t>
+          <t>0,33; 3,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,12</t>
+          <t>0,85; 3,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,08</t>
+          <t>1,01; 2,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,24</t>
+          <t>1,14; 3,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,74</t>
+          <t>0,82; 2,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,65</t>
+          <t>1,02; 2,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,92</t>
+          <t>0,83; 2,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,83</t>
+          <t>2,17; 5,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,42</t>
+          <t>0,41; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,55</t>
+          <t>0,77; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,0</t>
+          <t>1,25; 7,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,61</t>
+          <t>1,21; 5,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,76</t>
+          <t>1,79; 9,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,31</t>
+          <t>2,8; 8,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,34</t>
+          <t>1,19; 3,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,11</t>
+          <t>2,21; 5,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,45</t>
+          <t>1,08; 3,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,61</t>
+          <t>1,31; 5,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,78</t>
+          <t>1,15; 2,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,44</t>
+          <t>2,02; 4,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,31</t>
+          <t>1,54; 3,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,01</t>
+          <t>1,29; 3,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,44</t>
+          <t>1,89; 4,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,21</t>
+          <t>3,23; 6,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,83</t>
+          <t>2,18; 4,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,22</t>
+          <t>1,0; 3,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,99</t>
+          <t>1,68; 3,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,73</t>
+          <t>2,81; 4,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,46</t>
+          <t>2,01; 3,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,89</t>
+          <t>1,4; 2,84</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,2</t>
+          <t>1,58; 5,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,27</t>
+          <t>1,86; 4,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,62</t>
+          <t>1,08; 3,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,36</t>
+          <t>1,01; 3,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,91</t>
+          <t>1,21; 4,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,6</t>
+          <t>1,33; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,7</t>
+          <t>1,47; 3,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,26</t>
+          <t>2,75; 6,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,76</t>
+          <t>1,72; 3,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,57</t>
+          <t>1,77; 3,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,16</t>
+          <t>1,49; 3,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,74</t>
+          <t>2,37; 4,89</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,76</t>
+          <t>0,32; 2,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,2</t>
+          <t>1,1; 9,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,59</t>
+          <t>1,13; 2,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,62</t>
+          <t>1,78; 3,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,49</t>
+          <t>0,96; 2,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,45</t>
+          <t>1,59; 3,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,36</t>
+          <t>1,02; 2,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,12</t>
+          <t>1,5; 3,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,32</t>
+          <t>0,97; 2,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,26</t>
+          <t>1,76; 4,06</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,32</t>
+          <t>1,36; 2,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,52</t>
+          <t>2,27; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,61</t>
+          <t>1,55; 2,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,81</t>
+          <t>1,58; 2,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,74</t>
+          <t>1,73; 2,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,5</t>
+          <t>2,29; 3,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,87</t>
+          <t>1,78; 2,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,62</t>
+          <t>2,34; 3,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,38</t>
+          <t>1,69; 2,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,29</t>
+          <t>2,49; 3,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,55</t>
+          <t>1,83; 2,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,08</t>
+          <t>2,16; 3,05</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4546; 18651</t>
+          <t>4892; 19126</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5191; 22517</t>
+          <t>5124; 21824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7179; 23171</t>
+          <t>7387; 22005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3604; 14095</t>
+          <t>3875; 14397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>947; 8663</t>
+          <t>948; 9247</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2999; 15274</t>
+          <t>3659; 15254</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1109; 11714</t>
+          <t>1106; 12442</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11425; 28053</t>
+          <t>11742; 26326</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6812; 21852</t>
+          <t>7602; 23008</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11196; 32428</t>
+          <t>10911; 31418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10855; 28839</t>
+          <t>10779; 29730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17906; 35867</t>
+          <t>17529; 36131</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1008; 10742</t>
+          <t>1014; 10056</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3823; 15480</t>
+          <t>3225; 16033</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3136; 14396</t>
+          <t>3114; 14643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3413; 13523</t>
+          <t>3353; 13875</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4822; 17520</t>
+          <t>4966; 17923</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3103; 14731</t>
+          <t>3209; 13502</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1070; 11780</t>
+          <t>1226; 11627</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3192; 11950</t>
+          <t>3254; 12079</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7347; 22771</t>
+          <t>7448; 21538</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8791; 24362</t>
+          <t>8547; 24302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6426; 20547</t>
+          <t>6169; 20034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8387; 22107</t>
+          <t>8553; 22556</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4380; 15861</t>
+          <t>4515; 15674</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14070; 36533</t>
+          <t>13620; 36216</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2134; 12614</t>
+          <t>2165; 12520</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5451; 37057</t>
+          <t>5168; 39539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2244; 11752</t>
+          <t>2103; 12257</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3070; 14519</t>
+          <t>3146; 14484</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3056; 16213</t>
+          <t>2970; 15542</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4806; 13868</t>
+          <t>4669; 13476</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8520; 23712</t>
+          <t>8438; 22670</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19604; 45216</t>
+          <t>19599; 45080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7463; 23759</t>
+          <t>7400; 22870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9592; 46866</t>
+          <t>10950; 46144</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14528; 34386</t>
+          <t>14299; 34096</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24708; 51304</t>
+          <t>23328; 49549</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18086; 38030</t>
+          <t>17744; 38526</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13497; 31155</t>
+          <t>13343; 32089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13740; 31684</t>
+          <t>13466; 31770</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23061; 47518</t>
+          <t>24733; 49510</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19183; 39852</t>
+          <t>17965; 39219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9901; 31454</t>
+          <t>9766; 31989</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33448; 58414</t>
+          <t>32820; 59443</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54820; 91006</t>
+          <t>54068; 89672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39187; 68402</t>
+          <t>39695; 69470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27888; 58095</t>
+          <t>28103; 57068</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5415; 18191</t>
+          <t>5527; 17899</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9327; 26934</t>
+          <t>9492; 25352</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6332; 22460</t>
+          <t>6687; 22458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4843; 15890</t>
+          <t>4765; 16570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6856; 22248</t>
+          <t>6883; 23111</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9316; 27298</t>
+          <t>10068; 27871</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10409; 27326</t>
+          <t>10849; 27367</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22543; 52531</t>
+          <t>23074; 57017</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16055; 34503</t>
+          <t>15831; 34602</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21985; 45360</t>
+          <t>22418; 45098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20503; 42896</t>
+          <t>20285; 43470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31254; 62178</t>
+          <t>31047; 64125</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6848</t>
+          <t>0; 6856</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 9462</t>
+          <t>0; 7016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>932; 7936</t>
+          <t>933; 7992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2244; 22131</t>
+          <t>2649; 23872</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13912; 32353</t>
+          <t>14120; 33273</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19783; 39979</t>
+          <t>19703; 41214</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10295; 26970</t>
+          <t>10413; 27916</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12295; 26199</t>
+          <t>12078; 26039</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15694; 36489</t>
+          <t>15738; 36196</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20909; 42791</t>
+          <t>20571; 43176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12782; 31814</t>
+          <t>13282; 31347</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18237; 42661</t>
+          <t>17632; 40606</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45492; 75694</t>
+          <t>44609; 75916</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>76767; 120224</t>
+          <t>77511; 120940</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54543; 88346</t>
+          <t>52556; 85737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53864; 94792</t>
+          <t>53336; 97865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>58613; 92461</t>
+          <t>58568; 93290</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>82106; 123943</t>
+          <t>80971; 122577</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63334; 101227</t>
+          <t>62800; 100349</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>84086; 129461</t>
+          <t>83741; 130245</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>113043; 158522</t>
+          <t>112257; 156222</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171328; 228404</t>
+          <t>173005; 231659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125308; 176326</t>
+          <t>126693; 177745</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>151550; 214195</t>
+          <t>149790; 212179</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,04</t>
+          <t>1,04; 3,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,02</t>
+          <t>1,31; 5,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,13</t>
+          <t>1,68; 5,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,85</t>
+          <t>0,72; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,02</t>
+          <t>0,31; 3,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,85</t>
+          <t>0,94; 5,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,59</t>
+          <t>0,32; 3,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,88</t>
+          <t>2,75; 6,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,95</t>
+          <t>0,95; 2,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,19</t>
+          <t>1,42; 4,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,83</t>
+          <t>1,37; 3,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,79</t>
+          <t>1,88; 3,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,74</t>
+          <t>0,24; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,84</t>
+          <t>0,95; 3,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,88</t>
+          <t>0,79; 3,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,07</t>
+          <t>0,81; 3,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,82</t>
+          <t>1,33; 4,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,03</t>
+          <t>0,91; 3,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,12</t>
+          <t>0,34; 2,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,16</t>
+          <t>0,73; 2,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,92</t>
+          <t>1,0; 2,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,23</t>
+          <t>1,19; 3,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,67</t>
+          <t>0,78; 2,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,7</t>
+          <t>0,98; 2,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,89</t>
+          <t>0,79; 2,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,78</t>
+          <t>2,08; 5,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,4</t>
+          <t>0,4; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,92</t>
+          <t>2,75; 6,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,31</t>
+          <t>1,21; 7,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,59</t>
+          <t>1,22; 5,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,36</t>
+          <t>1,9; 10,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,07</t>
+          <t>2,76; 8,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,19</t>
+          <t>1,17; 3,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,09</t>
+          <t>2,27; 5,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,32</t>
+          <t>1,05; 3,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,53</t>
+          <t>3,14; 6,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,75</t>
+          <t>1,24; 2,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,28</t>
+          <t>2,13; 4,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,35</t>
+          <t>1,52; 3,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,1</t>
+          <t>1,51; 3,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,45</t>
+          <t>1,88; 4,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,47</t>
+          <t>3,03; 6,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,75</t>
+          <t>2,11; 4,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,27</t>
+          <t>2,09; 4,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,04</t>
+          <t>1,67; 3,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,67</t>
+          <t>2,78; 4,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,52</t>
+          <t>2,1; 3,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,84</t>
+          <t>1,95; 3,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,12</t>
+          <t>1,56; 5,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,97</t>
+          <t>2,02; 5,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,62</t>
+          <t>1,09; 3,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,5</t>
+          <t>0,9; 3,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,06</t>
+          <t>1,28; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,68</t>
+          <t>1,18; 3,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,71</t>
+          <t>1,4; 3,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,8</t>
+          <t>3,15; 5,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,77</t>
+          <t>1,72; 3,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,55</t>
+          <t>1,8; 3,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,2</t>
+          <t>1,42; 3,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,89</t>
+          <t>2,48; 4,09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,78</t>
+          <t>0,32; 2,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,93</t>
+          <t>0,73; 8,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,66</t>
+          <t>1,16; 2,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,73</t>
+          <t>1,7; 3,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,58</t>
+          <t>0,99; 2,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,43</t>
+          <t>1,77; 3,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,34</t>
+          <t>1,03; 2,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,15</t>
+          <t>1,53; 3,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,29</t>
+          <t>0,92; 2,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,06</t>
+          <t>1,92; 4,24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,32</t>
+          <t>1,36; 2,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,53</t>
+          <t>1,57; 2,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,9</t>
+          <t>1,85; 2,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,76</t>
+          <t>1,74; 2,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,46</t>
+          <t>2,37; 3,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,84</t>
+          <t>1,77; 2,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,64</t>
+          <t>2,79; 3,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,35</t>
+          <t>1,69; 2,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,33</t>
+          <t>2,42; 3,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,57</t>
+          <t>1,79; 2,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,05</t>
+          <t>2,46; 3,23</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>27937</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4892; 19126</t>
+          <t>4923; 18782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5124; 21824</t>
+          <t>5711; 22680</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7387; 22005</t>
+          <t>7200; 23825</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3875; 14397</t>
+          <t>3963; 15373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>948; 9247</t>
+          <t>942; 9538</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3659; 15254</t>
+          <t>2971; 16053</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1106; 12442</t>
+          <t>1113; 12893</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11742; 26326</t>
+          <t>13435; 29978</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7602; 23008</t>
+          <t>7400; 22669</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10911; 31418</t>
+          <t>10625; 30955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10779; 29730</t>
+          <t>10634; 29335</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17529; 36131</t>
+          <t>19585; 37846</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>14601</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1014; 10056</t>
+          <t>896; 9696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3225; 16033</t>
+          <t>3959; 16067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3114; 14643</t>
+          <t>2974; 14694</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3353; 13875</t>
+          <t>3925; 14694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4966; 17923</t>
+          <t>4936; 17643</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3209; 13502</t>
+          <t>3039; 13322</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1226; 11627</t>
+          <t>1251; 10978</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3254; 12079</t>
+          <t>3089; 12081</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7448; 21538</t>
+          <t>7358; 22045</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8547; 24302</t>
+          <t>8962; 24415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6169; 20034</t>
+          <t>5883; 21376</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8553; 22556</t>
+          <t>8905; 22007</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>30482</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4515; 15674</t>
+          <t>4301; 15269</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13620; 36216</t>
+          <t>13036; 37489</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2165; 12520</t>
+          <t>2070; 13129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5168; 39539</t>
+          <t>12970; 31642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2103; 12257</t>
+          <t>2038; 12388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3146; 14484</t>
+          <t>3152; 13938</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2970; 15542</t>
+          <t>3156; 17001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4669; 13476</t>
+          <t>5181; 15670</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8438; 22670</t>
+          <t>8319; 23343</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19599; 45080</t>
+          <t>20099; 45930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7400; 22870</t>
+          <t>7212; 23206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10950; 46144</t>
+          <t>20665; 41570</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>51626</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14299; 34096</t>
+          <t>15300; 34536</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23328; 49549</t>
+          <t>24593; 49783</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17744; 38526</t>
+          <t>17449; 38122</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13343; 32089</t>
+          <t>17063; 41473</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13466; 31770</t>
+          <t>13403; 30794</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24733; 49510</t>
+          <t>23219; 49297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17965; 39219</t>
+          <t>17418; 40197</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9766; 31989</t>
+          <t>17992; 35182</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32820; 59443</t>
+          <t>32514; 59166</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54068; 89672</t>
+          <t>53472; 90286</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39695; 69470</t>
+          <t>41431; 70849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28103; 57068</t>
+          <t>38793; 68254</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>44292</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5527; 17899</t>
+          <t>5455; 17983</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9492; 25352</t>
+          <t>10304; 26664</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6687; 22458</t>
+          <t>6770; 21148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4765; 16570</t>
+          <t>5112; 17312</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6883; 23111</t>
+          <t>7287; 24002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10068; 27871</t>
+          <t>8961; 27435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10849; 27367</t>
+          <t>10311; 27063</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23074; 57017</t>
+          <t>26184; 46174</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15831; 34602</t>
+          <t>15754; 36116</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22418; 45098</t>
+          <t>22803; 47065</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20285; 43470</t>
+          <t>19295; 42192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31047; 64125</t>
+          <t>34680; 57069</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>30327</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6856</t>
+          <t>0; 7047</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7016</t>
+          <t>0; 7809</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>933; 7992</t>
+          <t>924; 7840</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2649; 23872</t>
+          <t>1723; 20840</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14120; 33273</t>
+          <t>14534; 33409</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19703; 41214</t>
+          <t>18823; 40175</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10413; 27916</t>
+          <t>10751; 28491</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12078; 26039</t>
+          <t>14889; 31924</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15738; 36196</t>
+          <t>15988; 34972</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20571; 43176</t>
+          <t>20937; 43159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13282; 31347</t>
+          <t>12610; 33122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17632; 40606</t>
+          <t>20792; 45822</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74134</t>
+          <t>81016</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106252</t>
+          <t>118249</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>180386</t>
+          <t>199265</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44609; 75916</t>
+          <t>44589; 76267</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>77511; 120940</t>
+          <t>77377; 120989</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52556; 85737</t>
+          <t>53314; 88225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53336; 97865</t>
+          <t>63721; 102883</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>58568; 93290</t>
+          <t>58840; 95468</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80971; 122577</t>
+          <t>83766; 122769</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62800; 100349</t>
+          <t>62684; 98738</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>83741; 130245</t>
+          <t>101258; 137515</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>112257; 156222</t>
+          <t>112044; 158071</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>173005; 231659</t>
+          <t>168502; 229411</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126693; 177745</t>
+          <t>123887; 177038</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>149790; 212179</t>
+          <t>174200; 228541</t>
         </is>
       </c>
     </row>
